--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -40,13 +40,25 @@
     <x:t>Les Aigles</x:t>
   </x:si>
   <x:si>
+    <x:t>/uploads/logos/837f56a2-8c28-462c-94d6-929dc124d12f.png</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#1a3a5c</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#d58d10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>École Armand-Corbail</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>#1a3a5c</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#d58d10</x:t>
+    <x:t>#e8a020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Scorpions</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -440,6 +452,26 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" spans="1:6">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -46,19 +46,22 @@
     <x:t>#1a3a5c</x:t>
   </x:si>
   <x:si>
-    <x:t>#d58d10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>École Armand-Corbail</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>#e8a020</x:t>
+    <x:t>#c9a646</x:t>
+  </x:si>
+  <x:si>
+    <x:t>École Armand-Corbeil</x:t>
   </x:si>
   <x:si>
     <x:t>Les Scorpions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/logos/ccde6cd6-7342-4fd0-9274-890a0db77e5e.avif</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#0b2a5b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#f2b705</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -460,16 +463,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -58,10 +58,13 @@
     <x:t>/uploads/logos/ccde6cd6-7342-4fd0-9274-890a0db77e5e.avif</x:t>
   </x:si>
   <x:si>
+    <x:t>#f2b705</x:t>
+  </x:si>
+  <x:si>
     <x:t>#0b2a5b</x:t>
   </x:si>
   <x:si>
-    <x:t>#f2b705</x:t>
+    <x:t>[{"Type":"Site web","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Site web","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -415,7 +418,7 @@
   <x:dimension ref="A1:F1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -435,7 +438,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -454,8 +457,11 @@
       <x:c r="F2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
-    <x:row r="3" spans="1:6">
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -469,10 +475,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -49,6 +49,9 @@
     <x:t>#c9a646</x:t>
   </x:si>
   <x:si>
+    <x:t>[{"Type":"Facebook","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Instagram","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
+  </x:si>
+  <x:si>
     <x:t>École Armand-Corbeil</x:t>
   </x:si>
   <x:si>
@@ -62,9 +65,6 @@
   </x:si>
   <x:si>
     <x:t>#0b2a5b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[{"Type":"Site web","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Site web","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -458,7 +458,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
@@ -466,19 +466,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -61,10 +61,13 @@
     <x:t>/uploads/logos/ccde6cd6-7342-4fd0-9274-890a0db77e5e.avif</x:t>
   </x:si>
   <x:si>
-    <x:t>#f2b705</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#0b2a5b</x:t>
+    <x:t>#121212</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>#d8873b</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -475,9 +478,12 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="G3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -61,13 +61,13 @@
     <x:t>/uploads/logos/ccde6cd6-7342-4fd0-9274-890a0db77e5e.avif</x:t>
   </x:si>
   <x:si>
+    <x:t>#ffda24</x:t>
+  </x:si>
+  <x:si>
     <x:t>#121212</x:t>
   </x:si>
   <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>#d8873b</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -478,13 +478,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -43,10 +43,10 @@
     <x:t>/uploads/logos/837f56a2-8c28-462c-94d6-929dc124d12f.png</x:t>
   </x:si>
   <x:si>
-    <x:t>#1a3a5c</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#c9a646</x:t>
+    <x:t>#1c2f5c</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#e0be4a</x:t>
   </x:si>
   <x:si>
     <x:t>[{"Type":"Facebook","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Instagram","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
@@ -61,10 +61,10 @@
     <x:t>/uploads/logos/ccde6cd6-7342-4fd0-9274-890a0db77e5e.avif</x:t>
   </x:si>
   <x:si>
-    <x:t>#ffda24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#121212</x:t>
+    <x:t>#1f3a6d</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#e3b23c</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -478,10 +478,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>17</x:v>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -50,24 +50,6 @@
   </x:si>
   <x:si>
     <x:t>[{"Type":"Facebook","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Instagram","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>École Armand-Corbeil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Scorpions</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/logos/ccde6cd6-7342-4fd0-9274-890a0db77e5e.avif</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#1f3a6d</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#e3b23c</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -464,29 +446,6 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -43,13 +43,13 @@
     <x:t>/uploads/logos/837f56a2-8c28-462c-94d6-929dc124d12f.png</x:t>
   </x:si>
   <x:si>
-    <x:t>#1c2f5c</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#e0be4a</x:t>
+    <x:t>#e8a020</x:t>
   </x:si>
   <x:si>
     <x:t>[{"Type":"Facebook","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Instagram","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#1a3a5c</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -437,13 +437,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -22,7 +22,7 @@
     <x:t>Nom</x:t>
   </x:si>
   <x:si>
-    <x:t>CodeEcole</x:t>
+    <x:t>NomEquipe</x:t>
   </x:si>
   <x:si>
     <x:t>LogoPath</x:t>
@@ -34,22 +34,28 @@
     <x:t>CouleurSecondaire</x:t>
   </x:si>
   <x:si>
+    <x:t>LiensSociaux</x:t>
+  </x:si>
+  <x:si>
     <x:t>École de l'Amitié</x:t>
   </x:si>
   <x:si>
     <x:t>Les Aigles</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/logos/837f56a2-8c28-462c-94d6-929dc124d12f.png</x:t>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>#1a3a5c</x:t>
   </x:si>
   <x:si>
     <x:t>#e8a020</x:t>
   </x:si>
   <x:si>
-    <x:t>[{"Type":"Facebook","Url":"https://www.facebook.com/profile.php?id=100057229281252","Label":null},{"Type":"Instagram","Url":"https://www.instagram.com/aigles.rseq.amitie/","Label":null}]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#1a3a5c</x:t>
+    <x:t>Test année scolaire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Année scolaire</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -400,7 +406,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F1"/>
+  <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -422,28 +428,54 @@
       <x:c r="F1" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/ecoles.xlsx
+++ b/Data/ecoles.xlsx
@@ -37,7 +37,7 @@
     <x:t>LiensSociaux</x:t>
   </x:si>
   <x:si>
-    <x:t>École de l'Amitié</x:t>
+    <x:t>École de l'amitié</x:t>
   </x:si>
   <x:si>
     <x:t>Les Aigles</x:t>
@@ -52,10 +52,13 @@
     <x:t>#e8a020</x:t>
   </x:si>
   <x:si>
-    <x:t>Test année scolaire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Année scolaire</x:t>
+    <x:t>[{"Type":"Facebook","Url":"https://www.facebook.com/profile.php?id=61563902575511","Label":null}]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armand-Corbeil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Scorpions</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -452,7 +455,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
@@ -460,10 +463,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>9</x:v>
